--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.55681950709342</v>
+        <v>9.51548316990268</v>
       </c>
       <c r="D2" t="n">
-        <v>58.25988041165414</v>
+        <v>9.467230566893798</v>
       </c>
       <c r="E2" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F2" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.92925959417079</v>
+        <v>7.626004684052754</v>
       </c>
       <c r="D3" t="n">
-        <v>45.6248451540655</v>
+        <v>7.414037337535644</v>
       </c>
       <c r="E3" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F3" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.28848335721514</v>
+        <v>6.70937854554746</v>
       </c>
       <c r="D4" t="n">
-        <v>39.72042110523478</v>
+        <v>6.454568429600651</v>
       </c>
       <c r="E4" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F4" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.95721105034892</v>
+        <v>8.443046795681701</v>
       </c>
       <c r="D5" t="n">
-        <v>26.09757565515805</v>
+        <v>4.240856043963184</v>
       </c>
       <c r="E5" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F5" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.06569008018857</v>
+        <v>6.348174638030643</v>
       </c>
       <c r="D6" t="n">
-        <v>41.10248050158373</v>
+        <v>6.679153081507356</v>
       </c>
       <c r="E6" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F6" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.02866952177753</v>
+        <v>3.742158797288849</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97661381399168</v>
+        <v>4.058699744773648</v>
       </c>
       <c r="E7" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F7" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>64.16067598012128</v>
+        <v>10.42610984676971</v>
       </c>
       <c r="D8" t="n">
-        <v>9.548751144212419</v>
+        <v>1.551672060934518</v>
       </c>
       <c r="E8" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F8" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.53849140813448</v>
+        <v>7.075004853821852</v>
       </c>
       <c r="D9" t="n">
-        <v>45.20774440160788</v>
+        <v>7.346258465261281</v>
       </c>
       <c r="E9" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F9" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.77117268621996</v>
+        <v>6.137815561510744</v>
       </c>
       <c r="D10" t="n">
-        <v>37.81725838523004</v>
+        <v>6.145304487599882</v>
       </c>
       <c r="E10" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F10" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.29756057137496</v>
+        <v>6.223353592848431</v>
       </c>
       <c r="D11" t="n">
-        <v>36.88203602113963</v>
+        <v>5.99333085343519</v>
       </c>
       <c r="E11" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F11" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.69832132437512</v>
+        <v>6.613477215210956</v>
       </c>
       <c r="D12" t="n">
-        <v>14.31300885782608</v>
+        <v>2.325863939396738</v>
       </c>
       <c r="E12" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F12" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.22801389895106</v>
+        <v>5.237052258579547</v>
       </c>
       <c r="D13" t="n">
-        <v>31.0929945639459</v>
+        <v>5.05261161664121</v>
       </c>
       <c r="E13" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F13" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.61750080255599</v>
+        <v>4.650343880415349</v>
       </c>
       <c r="D14" t="n">
-        <v>28.9386147401659</v>
+        <v>4.702524895276958</v>
       </c>
       <c r="E14" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F14" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>52.68624186140665</v>
+        <v>8.561514302478582</v>
       </c>
       <c r="D15" t="n">
-        <v>36.27125486995885</v>
+        <v>5.894078916368312</v>
       </c>
       <c r="E15" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F15" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.06768787028517</v>
+        <v>3.74849927892134</v>
       </c>
       <c r="D16" t="n">
-        <v>23.49550241545709</v>
+        <v>3.818019142511777</v>
       </c>
       <c r="E16" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F16" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>45.58147435603252</v>
+        <v>7.406989582855285</v>
       </c>
       <c r="D17" t="n">
-        <v>46.39943442249601</v>
+        <v>7.539908093655603</v>
       </c>
       <c r="E17" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F17" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.10392317942973</v>
+        <v>2.941887516657332</v>
       </c>
       <c r="D18" t="n">
-        <v>18.35126167560236</v>
+        <v>2.982080022285384</v>
       </c>
       <c r="E18" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F18" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>49.95079247107927</v>
+        <v>8.117003776550382</v>
       </c>
       <c r="D19" t="n">
-        <v>50.39650507229925</v>
+        <v>8.189432074248629</v>
       </c>
       <c r="E19" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F19" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.86902224979911</v>
+        <v>5.016216115592355</v>
       </c>
       <c r="D20" t="n">
-        <v>32.56767859368865</v>
+        <v>5.292247771474407</v>
       </c>
       <c r="E20" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F20" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13.33709674161589</v>
+        <v>2.167278220512582</v>
       </c>
       <c r="D21" t="n">
-        <v>12.88661461921283</v>
+        <v>2.094074875622085</v>
       </c>
       <c r="E21" t="n">
-        <v>13.13675228700426</v>
+        <v>2.134722246638192</v>
       </c>
       <c r="F21" t="n">
-        <v>12.90236905976126</v>
+        <v>2.096634972211205</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
